--- a/artfynd/A 2962-2023 artfynd.xlsx
+++ b/artfynd/A 2962-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2962-2023 artfynd.xlsx
+++ b/artfynd/A 2962-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106840527</v>
+        <v>106895210</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505386.6427459326</v>
+        <v>505362</v>
       </c>
       <c r="R2" t="n">
-        <v>7005369.028491905</v>
+        <v>7005838</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,24 +746,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lunglav på en sälgstubbe. Obs! Fyndplatsen ligger inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +773,27 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Flerskiktad luckig grandominerad skog med inslag av tall, björk och sälg med träd av olika ålder. Mestadels träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand. Fyndplatsen finns på frisk-fuktig och fuktig mark som angränsar till ett vattendrag.</t>
+          <t>Grandominerad, flerskiktad och luckig skog med inslag av tall, björk och gråal på frisk och frisk-fuktig mark. Regelbunden förekomst av block där flertalet block har över två meters höjd. Kolad ved indikerar här tidigare brand.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>En stubbe av en knäckt sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En stubbe av en knäckt sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -835,19 +811,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106896557</v>
+        <v>106895590</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -878,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505431.5136382245</v>
+        <v>505400</v>
       </c>
       <c r="R3" t="n">
-        <v>7005849.157069448</v>
+        <v>7005806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,24 +882,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Långväxt garnlav på gran intill ett större block. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,12 +904,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Grandominerad, flerskiktad och luckig skog med inslag av tall, björk och gråal på frisk och frisk-fuktig mark. Fältskikt med ris och inslag av örter och gräs. Regelbunden förekomst av större block. Kolad ved indikerar här tidigare brand.</t>
+          <t>Talldominerad, flerskiktad och ljusöppen skog med inslag av gran och björk på frisk och frisk-fuktig mark. Glest buskskikt med enbuskar. Regelbunden förekomst av block där flertalet block har över två meters höjd. Kolad ved indikerar här tidigare brand.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -961,11 +922,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM3" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -973,7 +929,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -991,19 +947,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106907566</v>
+        <v>106896480</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1034,13 +985,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505234.8531307225</v>
+        <v>505410</v>
       </c>
       <c r="R4" t="n">
-        <v>7005823.544562514</v>
+        <v>7005863</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1067,24 +1018,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på ett flertal granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1104,7 +1045,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall, björk, gråal och sälg och med träd av olika ålder på frisk-fuktig och fuktig mark. Kolade stubbar indikerar här tidigare brand. Här förekommer även stora block med upp till omkring 2 meters höjd.</t>
+          <t>Grandominerad, flerskiktad och luckig skog med inslag av tall, björk och gråal på frisk och frisk-fuktig mark. Fältskikt med ris och inslag av örter och gräs. Regelbunden förekomst av större block. Kolad ved indikerar här tidigare brand.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1117,11 +1058,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM4" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -1129,7 +1065,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1147,19 +1083,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106904197</v>
+        <v>106896557</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1190,10 +1121,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505361.5971924919</v>
+        <v>505432</v>
       </c>
       <c r="R5" t="n">
-        <v>7005472.409834298</v>
+        <v>7005849</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1223,24 +1154,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikliga mängder med långväxt garnlav på ett flertal granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1260,7 +1181,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall och björk och med träd av olika ålder på frisk och frisk-fuktig mark. Gott om träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand. Myrstackar förekommer.</t>
+          <t>Grandominerad, flerskiktad och luckig skog med inslag av tall, björk och gråal på frisk och frisk-fuktig mark. Fältskikt med ris och inslag av örter och gräs. Regelbunden förekomst av större block. Kolad ved indikerar här tidigare brand.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1303,19 +1224,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106902130</v>
+        <v>106897703</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1346,10 +1262,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505402.4429668278</v>
+        <v>505400</v>
       </c>
       <c r="R6" t="n">
-        <v>7005386.216982934</v>
+        <v>7005737</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1379,24 +1295,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Enstaka långväxta bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1411,12 +1317,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall, björk och sälg med träd av olika ålder. Mestadels träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand. Fyndplatsen finns på frisk och frisk-fuktig mark som angränsar till ett vattendrag.</t>
+          <t>Luckig barrskog med gran, tall och inslag av björk och gråal på fuktig och frisk-fuktig mark som angränsar till myrmark. Buskskikt med enbuskar och fältskikt dominerat av risväxter. Regelbunden förekomst av större block. Kolad ved indikerar här tidigare brand.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1454,19 +1360,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106904753</v>
+        <v>106897822</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1497,10 +1398,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505225.3429920978</v>
+        <v>505351</v>
       </c>
       <c r="R7" t="n">
-        <v>7005552.574316284</v>
+        <v>7005667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1530,24 +1431,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Enstaka långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Garnlav på en stam av tall. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1562,32 +1453,32 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall och björk och med träd av olika ålder på frisk och frisk-fuktig mark. Gott om träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand.</t>
+          <t>Talldominerad, flerskiktad och ljusöppen skog med inslag av gran och björk på frisk och frisk-fuktig mark. Glest buskskikt med enbuskar. Regelbunden förekomst av större block. Kolad ved indikerar här tidigare brand.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1605,19 +1496,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106896480</v>
+        <v>106897956</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1648,13 +1534,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505409.3330305539</v>
+        <v>505347</v>
       </c>
       <c r="R8" t="n">
-        <v>7005863.118477867</v>
+        <v>7005616</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1681,24 +1567,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Enstaka långväxta bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1713,12 +1589,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grandominerad, flerskiktad och luckig skog med inslag av tall, björk och gråal på frisk och frisk-fuktig mark. Fältskikt med ris och inslag av örter och gräs. Regelbunden förekomst av större block. Kolad ved indikerar här tidigare brand.</t>
+          <t>Luckig barrskog med tall, gran och inslag av björk på frisk mark som angränsar till myrmark. Risdominerat fältskikt. Förekomst av större block där vissa block är över 2 meter i diameter. Kolad ved indikerar här tidigare brand.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1756,19 +1632,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106906881</v>
+        <v>106901903</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1799,13 +1670,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505190.989168068</v>
+        <v>505389</v>
       </c>
       <c r="R9" t="n">
-        <v>7005824.376953143</v>
+        <v>7005384</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1832,24 +1703,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Långväxt garnlav på gran och även på björk. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1869,7 +1730,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall, björk, gråal och sälg och med träd av olika ålder på frisk-fuktig och frisk mark. Kolade stubbar indikerar här tidigare brand. Här förekommer även stora block med upp till omkring 2 meters höjd.</t>
+          <t>Flerskiktad, luckig, grandominerad skog med inslag av tall, björk och sälg med träd av olika ålder. Mestadels träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand. Fyndplatsen finns på frisk och frisk-fuktig mark som angränsar till ett vattendrag.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1884,7 +1745,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>Här växer garnlav även på björk.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1894,7 +1755,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies # Här växer garnlav även på björk.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1912,19 +1773,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106897822</v>
+        <v>106902130</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1955,13 +1811,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505350.8726725657</v>
+        <v>505403</v>
       </c>
       <c r="R10" t="n">
-        <v>7005667.486695948</v>
+        <v>7005386</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1988,24 +1844,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Garnlav på en stam av tall. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2020,32 +1866,32 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Talldominerad, flerskiktad och ljusöppen skog med inslag av gran och björk på frisk och frisk-fuktig mark. Glest buskskikt med enbuskar. Regelbunden förekomst av större block. Kolad ved indikerar här tidigare brand.</t>
+          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall, björk och sälg med träd av olika ålder. Mestadels träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand. Fyndplatsen finns på frisk och frisk-fuktig mark som angränsar till ett vattendrag.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2066,16 +1912,11 @@
         <v>106902524</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2106,10 +1947,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505421.9451077728</v>
+        <v>505422</v>
       </c>
       <c r="R11" t="n">
-        <v>7005353.280218472</v>
+        <v>7005353</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2139,19 +1980,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2222,16 +2053,11 @@
         <v>106902893</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2262,10 +2088,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505363.5785185107</v>
+        <v>505364</v>
       </c>
       <c r="R12" t="n">
-        <v>7005368.538501659</v>
+        <v>7005369</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2295,19 +2121,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2370,47 +2186,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106904873</v>
+        <v>106903095</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2418,13 +2224,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505347.9956191682</v>
+        <v>505365</v>
       </c>
       <c r="R13" t="n">
-        <v>7005493.161824665</v>
+        <v>7005452</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2451,24 +2257,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack-spår av tretåig hackspett. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2477,6 +2273,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2500,14 +2297,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Ringhack på en granstam. # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2525,19 +2327,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106903095</v>
+        <v>106904197</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2568,13 +2365,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505364.7958547555</v>
+        <v>505361</v>
       </c>
       <c r="R14" t="n">
-        <v>7005452.54373296</v>
+        <v>7005473</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2601,24 +2398,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Rikliga mängder med långväxt garnlav på ett flertal granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2681,19 +2468,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106901903</v>
+        <v>106904520</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2724,13 +2506,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505388.4269179855</v>
+        <v>505348</v>
       </c>
       <c r="R15" t="n">
-        <v>7005383.935418255</v>
+        <v>7005493</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2757,24 +2539,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran och även på björk. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2794,7 +2566,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Flerskiktad, luckig, grandominerad skog med inslag av tall, björk och sälg med träd av olika ålder. Mestadels träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand. Fyndplatsen finns på frisk och frisk-fuktig mark som angränsar till ett vattendrag.</t>
+          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall och björk och med träd av olika ålder på frisk och frisk-fuktig mark. Gott om träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand. Myrstackar förekommer.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2807,11 +2579,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Här växer garnlav även på björk.</t>
-        </is>
-      </c>
       <c r="AM15" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -2819,7 +2586,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Här växer garnlav även på björk.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2837,43 +2604,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106896000</v>
+        <v>106904753</v>
       </c>
       <c r="B16" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2881,13 +2642,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505399.5026502781</v>
+        <v>505226</v>
       </c>
       <c r="R16" t="n">
-        <v>7005792.656801357</v>
+        <v>7005553</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2914,24 +2675,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Revlummer intill en kolad brandpåverkad stubbe.</t>
+          <t>Enstaka långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2946,12 +2697,32 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Talldominerad, flerskiktad och ljusöppen skog med inslag av gran och björk på frisk och frisk-fuktig mark. Glest buskskikt med enbuskar. Regelbunden förekomst av block där flertalet block har över två meters höjd. Kolad ved indikerar här tidigare brand.</t>
+          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall och björk och med träd av olika ålder på frisk och frisk-fuktig mark. Gott om träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2969,19 +2740,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106897703</v>
+        <v>106905087</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -3012,10 +2778,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505400.0484083994</v>
+        <v>505127</v>
       </c>
       <c r="R17" t="n">
-        <v>7005736.661688886</v>
+        <v>7005698</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -3045,24 +2811,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka långväxta bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Enstaka långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3077,12 +2833,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Luckig barrskog med gran, tall och inslag av björk och gråal på fuktig och frisk-fuktig mark som angränsar till myrmark. Buskskikt med enbuskar och fältskikt dominerat av risväxter. Regelbunden förekomst av större block. Kolad ved indikerar här tidigare brand.</t>
+          <t>Flerskiktad, luckig och talldominerad skog med inslag av gran och björk och med träd av olika ålder på frisk och frisk-fuktig mark. Fyndplatsen ligger på sluttande mark med stora block alt. berg i dagen. Kolade stubbar indikerar här tidigare brand.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3120,19 +2876,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106904520</v>
+        <v>106905827</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -3163,13 +2914,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505347.9956191682</v>
+        <v>505163</v>
       </c>
       <c r="R18" t="n">
-        <v>7005493.161824665</v>
+        <v>7005867</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3196,24 +2947,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Enstaka bålar av garnlav.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3233,17 +2974,22 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall och björk och med träd av olika ålder på frisk och frisk-fuktig mark. Gott om träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand. Myrstackar förekommer.</t>
+          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall, björk, gråal och sälg och med träd av olika ålder på frisk mark. Kolade stubbar indikerar här tidigare brand. Här förekommer även stora block med över 2 meters höjd.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>gråal</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Yngre träd med ca 2-3 meters höjd som står under några större granar mellan ett par stora block.</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -3253,7 +2999,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Alnus incana # Yngre träd med ca 2-3 meters höjd som står under några större granar mellan ett par stora block.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3271,19 +3017,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>106905087</v>
+        <v>106906881</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -3314,13 +3055,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505126.5271779827</v>
+        <v>505191</v>
       </c>
       <c r="R19" t="n">
-        <v>7005697.37972659</v>
+        <v>7005824</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3347,24 +3088,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3379,12 +3110,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Flerskiktad, luckig och talldominerad skog med inslag av gran och björk och med träd av olika ålder på frisk och frisk-fuktig mark. Fyndplatsen ligger på sluttande mark med stora block alt. berg i dagen. Kolade stubbar indikerar här tidigare brand.</t>
+          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall, björk, gråal och sälg och med träd av olika ålder på frisk-fuktig och frisk mark. Kolade stubbar indikerar här tidigare brand. Här förekommer även stora block med upp till omkring 2 meters höjd.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3397,6 +3128,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM19" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -3404,7 +3140,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3422,46 +3158,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106906104</v>
+        <v>106907566</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3469,10 +3196,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505190.0565034206</v>
+        <v>505235</v>
       </c>
       <c r="R20" t="n">
-        <v>7005841.986731392</v>
+        <v>7005824</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3502,24 +3229,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Långväxt garnlav på ett flertal granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3539,32 +3256,32 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall, björk, gråal och sälg och med träd av olika ålder på frisk-fuktig och frisk mark. Kolade stubbar indikerar här tidigare brand. Här förekommer även stora block med upp till omkring 2 meters höjd.</t>
+          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall, björk, gråal och sälg och med träd av olika ålder på frisk-fuktig och fuktig mark. Kolade stubbar indikerar här tidigare brand. Här förekommer även stora block med upp till omkring 2 meters höjd.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>En låga av sälg.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En låga av sälg.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3585,16 +3302,11 @@
         <v>106907986</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3625,10 +3337,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505263.7793697227</v>
+        <v>505264</v>
       </c>
       <c r="R21" t="n">
-        <v>7005832.171414716</v>
+        <v>7005832</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3658,19 +3370,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3738,15 +3440,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>106895590</v>
+        <v>106832583</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3754,26 +3451,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3781,13 +3482,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505400.3851573077</v>
+        <v>505385</v>
       </c>
       <c r="R22" t="n">
-        <v>7005805.753980736</v>
+        <v>7005435</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3814,24 +3515,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran intill ett större block. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Välmående lunglav på en grov gammal sälg där det även växer stuplav.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3846,32 +3537,37 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Talldominerad, flerskiktad och ljusöppen skog med inslag av gran och björk på frisk och frisk-fuktig mark. Glest buskskikt med enbuskar. Regelbunden förekomst av block där flertalet block har över två meters höjd. Kolad ved indikerar här tidigare brand.</t>
+          <t>Ett skogsbestånd med gran, tall och gott om björk samt enstaka grov sälg på frisk-fuktig och frisk mark. Merparten av träden är av smalare dimensioner.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>En gammal sälg med 58 cm i brösthöjdsdiameter. Sälgen har vissa skador med död ved och är angripen av vedsvamp.</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov fårad bark. # Salix caprea # En gammal sälg med 58 cm i brösthöjdsdiameter. Sälgen har vissa skador med död ved och är angripen av vedsvamp.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3889,15 +3585,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106897956</v>
+        <v>106840527</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3905,26 +3596,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3932,13 +3627,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505346.4349614474</v>
+        <v>505387</v>
       </c>
       <c r="R23" t="n">
-        <v>7005616.448787925</v>
+        <v>7005369</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3965,24 +3660,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Enstaka långväxta bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Lunglav på en sälgstubbe. Obs! Fyndplatsen ligger inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3997,32 +3682,37 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Luckig barrskog med tall, gran och inslag av björk på frisk mark som angränsar till myrmark. Risdominerat fältskikt. Förekomst av större block där vissa block är över 2 meter i diameter. Kolad ved indikerar här tidigare brand.</t>
+          <t>Flerskiktad luckig grandominerad skog med inslag av tall, björk och sälg med träd av olika ålder. Mestadels träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand. Fyndplatsen finns på frisk-fuktig och fuktig mark som angränsar till ett vattendrag.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>En stubbe av en knäckt sälg.</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En stubbe av en knäckt sälg.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -4040,15 +3730,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>106902755</v>
+        <v>106906104</v>
       </c>
       <c r="B24" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4056,45 +3741,44 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norr om Mellansjöån, Ösjön, Lit, Jmt</t>
+          <t>Norr om Mellansjöån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505283.4984623663</v>
+        <v>505190</v>
       </c>
       <c r="R24" t="n">
-        <v>7005387.37526797</v>
+        <v>7005842</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -4121,24 +3805,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack-spår av tretåig hackspett. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Lunglav på en sälglåga. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4147,6 +3821,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -4157,27 +3832,32 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall, björk och sälg med träd av olika ålder. Mestadels träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand. Fyndplatsen finns på frisk och frisk-fuktig mark som angränsar till ett vattendrag. Här finns även äldre spår av bäver.</t>
+          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall, björk, gråal och sälg och med träd av olika ålder på frisk-fuktig och frisk mark. Kolade stubbar indikerar här tidigare brand. Här förekommer även stora block med upp till omkring 2 meters höjd.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>En låga av sälg.</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En låga av sälg.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4195,37 +3875,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>106895210</v>
+        <v>106905956</v>
       </c>
       <c r="B25" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -4238,10 +3913,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505361.8947790654</v>
+        <v>505163</v>
       </c>
       <c r="R25" t="n">
-        <v>7005838.203135551</v>
+        <v>7005867</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4271,24 +3946,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+          <t>Norrlandslav på ett stort moss- och lavtäckt block.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4308,27 +3973,17 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Grandominerad, flerskiktad och luckig skog med inslag av tall, björk och gråal på frisk och frisk-fuktig mark. Regelbunden förekomst av block där flertalet block har över två meters höjd. Kolad ved indikerar här tidigare brand.</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall, björk, gråal och sälg och med träd av olika ålder på frisk mark. Kolade stubbar indikerar här tidigare brand. Här förekommer även stora block med över 2 meters höjd.</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Block (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Rock (&gt; 200 mm) # Stort block med diameter på över 2 meter.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4343,6 +3998,672 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>106834575</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norr om Mellansjöån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>505385</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7005435</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Stuplav på en grov gammal sälg där det även växer lunglav.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Ett skogsbestånd med gran, tall och gott om björk samt enstaka grov sälg på frisk-fuktig och frisk mark. Merparten av träden är av smalare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>En gammal sälg med 58 cm i brösthöjdsdiameter. Sälgen har vissa skador med död ved och är angripen av vedsvamp.</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov fårad bark. # Salix caprea # En gammal sälg med 58 cm i brösthöjdsdiameter. Sälgen har vissa skador med död ved och är angripen av vedsvamp.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>106902755</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norr om Mellansjöån, Ösjön, Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>505284</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7005388</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack-spår av tretåig hackspett. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall, björk och sälg med träd av olika ålder. Mestadels träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand. Fyndplatsen finns på frisk och frisk-fuktig mark som angränsar till ett vattendrag. Här finns även äldre spår av bäver.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>106904873</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Norr om Mellansjöån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>505348</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7005493</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack-spår av tretåig hackspett. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Äldre, flerskiktad, luckig och grandominerad skog med inslag av tall och björk och med träd av olika ålder på frisk och frisk-fuktig mark. Gott om träd med smalare dimensioner. Kolade stubbar indikerar här tidigare brand. Myrstackar förekommer.</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Ringhack på en granstam. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>106895207</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norr om Mellansjöån, Ösjön, Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>505323</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7005849</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gott om tjäderspillning på snön nedanför en tall. Spillningens längd upp till 6-7 cm. Obs! Fyndplatsen ligger inom en avverkningsanmäld yta med beteckning A 2962-2023.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Grandominerad, flerskiktad och luckig skog med inslag av tall, björk och gråal på frisk och frisk-fuktig mark. Regelbunden förekomst av block där flertalet block har över två meters höjd. Kolad ved indikerar här tidigare brand.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>106896000</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norr om Mellansjöån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>505399</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7005793</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Revlummer intill en kolad brandpåverkad stubbe.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Talldominerad, flerskiktad och ljusöppen skog med inslag av gran och björk på frisk och frisk-fuktig mark. Glest buskskikt med enbuskar. Regelbunden förekomst av block där flertalet block har över två meters höjd. Kolad ved indikerar här tidigare brand.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2962-2023 artfynd.xlsx
+++ b/artfynd/A 2962-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106895210</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -944,6 +954,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106895590</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1080,6 +1095,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106896480</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1221,6 +1241,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106896557</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1357,6 +1382,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106897703</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1493,6 +1523,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106897822</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1629,6 +1664,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106897956</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1770,6 +1810,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106901903</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1906,6 +1951,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106902130</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2047,6 +2097,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106902524</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2183,6 +2238,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106902893</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2324,6 +2384,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106903095</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2465,6 +2530,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106904197</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2601,6 +2671,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106904520</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2737,6 +2812,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106904753</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2873,6 +2953,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106905087</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3014,6 +3099,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106905827</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3155,6 +3245,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106906881</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3296,6 +3391,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106907566</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3437,6 +3537,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106907986</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3582,6 +3687,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106832583</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3727,6 +3837,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106840527</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3872,6 +3987,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106906104</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3998,6 +4118,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106905956</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4143,6 +4268,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106834575</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4283,6 +4413,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106902755</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4423,6 +4558,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106904873</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4547,6 +4687,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106895207</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4664,8 +4809,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106896000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>